--- a/output/水戸赤十字病院_随意契約_X線関連.xlsx
+++ b/output/水戸赤十字病院_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -658,7 +658,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>X線一般撮影装置修理について</t>
+          <t>Ｘ線透視撮影装置における医用画像情報システムの接続にかかる契約</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
@@ -669,33 +669,75 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>令和7年12月16日</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>富士フイルムメディカル株式会社 東京支店東京都江東区有明3-5-7TOC有明イーストタワー14階</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2189000</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>透視撮影台（X線テレビ）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>X線一般撮影装置修理について</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>財務課調度管財室茨城県水戸市三の丸3-12-48</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>令和8年2月10日</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>島津メディカルシステムズ株式会社茨城県牛久市中央4-24-2アルシェビル102号</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>1650000</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>https://mito.jrc.or.jp/data/media/mito-jrc/uploads/2026/04/MHP_2604015/MHP_2604015.pdf</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -758,7 +800,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
     </row>
